--- a/詳細設計図/タスク編集機能_詳細設計図.xlsx
+++ b/詳細設計図/タスク編集機能_詳細設計図.xlsx
@@ -842,15 +842,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>81000</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>116640</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>142200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>1105920</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>43920</xdr:rowOff>
+      <xdr:colOff>1036800</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>10800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -863,8 +863,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="81000" y="1193040"/>
-          <a:ext cx="9176400" cy="5594760"/>
+          <a:off x="0" y="1542240"/>
+          <a:ext cx="9188280" cy="5536080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -891,9 +891,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>871560</xdr:colOff>
+      <xdr:colOff>871200</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>3438360</xdr:rowOff>
+      <xdr:rowOff>3438000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -907,7 +907,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="523800" y="1651320"/>
-          <a:ext cx="8052840" cy="4930200"/>
+          <a:ext cx="8052480" cy="4929840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -934,9 +934,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>217440</xdr:colOff>
+      <xdr:colOff>217080</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>3513240</xdr:rowOff>
+      <xdr:rowOff>3512880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -950,7 +950,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="693360" y="1716120"/>
-          <a:ext cx="8069400" cy="4940280"/>
+          <a:ext cx="8069040" cy="4939920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -977,9 +977,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>515880</xdr:colOff>
+      <xdr:colOff>515520</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>3577680</xdr:rowOff>
+      <xdr:rowOff>3577320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -993,7 +993,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="429840" y="1677600"/>
-          <a:ext cx="8237520" cy="5043240"/>
+          <a:ext cx="8237160" cy="5042880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/詳細設計図/タスク編集機能_詳細設計図.xlsx
+++ b/詳細設計図/タスク編集機能_詳細設計図.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,12 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="95">
   <si>
     <t xml:space="preserve">プロジェクト型演習　成果ドキュメント</t>
   </si>
   <si>
-    <t xml:space="preserve">○○○○システム</t>
+    <t xml:space="preserve">MyTaskSystem</t>
   </si>
   <si>
     <t xml:space="preserve">初版</t>
@@ -60,9 +60,6 @@
     <t xml:space="preserve">承認印</t>
   </si>
   <si>
-    <t xml:space="preserve">MyTaskSystem</t>
-  </si>
-  <si>
     <t xml:space="preserve">タスク編集機能</t>
   </si>
   <si>
@@ -90,8 +87,9 @@
     <t xml:space="preserve">事前条件</t>
   </si>
   <si>
-    <t xml:space="preserve">ログイン状態であること
-登録済みのタスクがあること</t>
+    <t xml:space="preserve">・ログイン状態であること
+・タスクが登録されていること
+・タスクの担当者がログイン中のユーザーであること</t>
   </si>
   <si>
     <t xml:space="preserve">イベントフロー</t>
@@ -132,7 +130,18 @@
       </rPr>
       <t xml:space="preserve">③ユーザーは、「更新する」ボタンを押下する。
 ④システムは、入力された情報をチェックする。(Alt-2)
-⑤システムは、入力された情報を更新する。</t>
+⑤システムは、入力された情報を更新する。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS PGothic"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">⑥システムは、[タスク編集完了画面]に遷移する。</t>
     </r>
   </si>
   <si>
@@ -148,8 +157,28 @@
     <t xml:space="preserve">例外フロー</t>
   </si>
   <si>
-    <t xml:space="preserve">Alt-2：「期限」「メモ」以外にNULLが含まれていた場合
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS PGothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Alt-2：「期限」「メモ」以外にNULLが含まれていた場合
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS PGothic"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">　　　　また、「タスク名」「メモ」に最大文字数+1文字以上の文字が入力された場合（タスク名：51以上,メモ：101以上）
 1.エラー画面に遷移する</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">事後条件</t>
@@ -357,9 +386,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="m\月d\日"/>
+    <numFmt numFmtId="166" formatCode="m\月d\日"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -592,7 +622,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -621,6 +651,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -645,7 +679,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -848,9 +882,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>1036800</xdr:colOff>
+      <xdr:colOff>1036080</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>10800</xdr:rowOff>
+      <xdr:rowOff>10080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -864,7 +898,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="1542240"/>
-          <a:ext cx="9188280" cy="5536080"/>
+          <a:ext cx="9187560" cy="5535360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -891,9 +925,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>871200</xdr:colOff>
+      <xdr:colOff>870480</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>3438000</xdr:rowOff>
+      <xdr:rowOff>3437280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -907,7 +941,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="523800" y="1651320"/>
-          <a:ext cx="8052480" cy="4929840"/>
+          <a:ext cx="8051760" cy="4929120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -934,9 +968,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>217080</xdr:colOff>
+      <xdr:colOff>216360</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>3512880</xdr:rowOff>
+      <xdr:rowOff>3512160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -950,7 +984,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="693360" y="1716120"/>
-          <a:ext cx="8069040" cy="4939920"/>
+          <a:ext cx="8068320" cy="4939200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -977,9 +1011,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>515520</xdr:colOff>
+      <xdr:colOff>514800</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>3577320</xdr:rowOff>
+      <xdr:rowOff>3576600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -993,7 +1027,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="429840" y="1677600"/>
-          <a:ext cx="8237160" cy="5042880"/>
+          <a:ext cx="8236440" cy="5042160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1323,9 +1357,11 @@
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
+      <c r="I14" s="7" t="n">
+        <v>45708</v>
+      </c>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G15" s="6"/>
@@ -1335,19 +1371,19 @@
       <c r="K15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2368,218 +2404,218 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="10" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10" t="s">
+      <c r="E1" s="11"/>
+      <c r="F1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10" t="s">
+      <c r="G1" s="11"/>
+      <c r="H1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="12" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="12" t="s">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="13"/>
+      <c r="H2" s="14" t="n">
+        <v>45707</v>
+      </c>
+      <c r="I2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="12"/>
-      <c r="H2" s="13" t="n">
-        <v>45707</v>
-      </c>
-      <c r="I2" s="12" t="s">
+      <c r="J2" s="15"/>
+    </row>
+    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="15"/>
+    </row>
+    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="15"/>
+    </row>
+    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="14"/>
-    </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="14"/>
-    </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="14"/>
-    </row>
-    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15" t="s">
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="16" t="s">
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+    </row>
+    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-    </row>
-    <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="18" t="s">
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+    </row>
+    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-    </row>
-    <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="18" t="s">
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+    </row>
+    <row r="8" customFormat="false" ht="41" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-    </row>
-    <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="19" t="s">
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+    </row>
+    <row r="9" customFormat="false" ht="74" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-    </row>
-    <row r="9" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
+      <c r="B9" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="C9" s="22"/>
+      <c r="D9" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="21"/>
-      <c r="D9" s="19" t="s">
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+    </row>
+    <row r="10" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21"/>
+      <c r="B10" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-    </row>
-    <row r="10" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20"/>
-      <c r="B10" s="21" t="s">
+      <c r="C10" s="22"/>
+      <c r="D10" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="19" t="s">
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+    </row>
+    <row r="11" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21"/>
+      <c r="B11" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-    </row>
-    <row r="11" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20"/>
-      <c r="B11" s="21" t="s">
+      <c r="C11" s="22"/>
+      <c r="D11" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="21"/>
-      <c r="D11" s="19" t="s">
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+    </row>
+    <row r="12" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-    </row>
-    <row r="12" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="s">
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="22" t="s">
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="23"/>
+    </row>
+    <row r="13" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-    </row>
-    <row r="13" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="23" t="s">
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3623,564 +3659,564 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="10" t="s">
+      <c r="A1" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10" t="s">
+      <c r="E1" s="11"/>
+      <c r="F1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="10"/>
-      <c r="H1" s="26" t="s">
+      <c r="G1" s="11"/>
+      <c r="H1" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="27" t="s">
+      <c r="J1" s="28" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="25"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="12" t="s">
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="13"/>
+      <c r="H2" s="14" t="n">
+        <v>45707</v>
+      </c>
+      <c r="I2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="12"/>
-      <c r="H2" s="13" t="n">
-        <v>45707</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="14"/>
+      <c r="J2" s="15"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="25"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="14"/>
+      <c r="A3" s="26"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="25"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="14"/>
+      <c r="A4" s="26"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="28"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
+      <c r="A5" s="29"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="28"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
+      <c r="A6" s="29"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="28"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
+      <c r="A7" s="29"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="28"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
+      <c r="A8" s="29"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="28"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
+      <c r="A9" s="29"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="28"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="28"/>
+      <c r="A10" s="29"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="28"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="28"/>
+      <c r="A11" s="29"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="28"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28"/>
+      <c r="A12" s="29"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="28"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28"/>
+      <c r="A13" s="29"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="28"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="28"/>
-      <c r="J14" s="28"/>
+      <c r="A14" s="29"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="28"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="28"/>
+      <c r="A15" s="29"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
     </row>
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="28"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="28"/>
+      <c r="A16" s="29"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="28"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="28"/>
+      <c r="A17" s="29"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="28"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28"/>
+      <c r="A18" s="29"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="28"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
+      <c r="A19" s="29"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="28"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
+      <c r="A20" s="29"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="28"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
-      <c r="J21" s="28"/>
+      <c r="A21" s="29"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="29"/>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="28"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="28"/>
+      <c r="A22" s="29"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="28"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
+      <c r="A23" s="29"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="28"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="28"/>
+      <c r="A24" s="29"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29"/>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="28"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="28"/>
+      <c r="A25" s="29"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="28"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
+      <c r="A26" s="29"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="28"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28"/>
-      <c r="J27" s="28"/>
+      <c r="A27" s="29"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="28"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="28"/>
+      <c r="A28" s="29"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="28"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
-      <c r="J29" s="28"/>
+      <c r="A29" s="29"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="28"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="28"/>
-      <c r="J30" s="28"/>
+      <c r="A30" s="29"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="28"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="28"/>
-      <c r="J31" s="28"/>
+      <c r="A31" s="29"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="28"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
+      <c r="A32" s="29"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="28"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28"/>
-      <c r="J33" s="28"/>
+      <c r="A33" s="29"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="29"/>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="28"/>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="28"/>
-      <c r="J34" s="28"/>
+      <c r="A34" s="29"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="29"/>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="28"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="28"/>
-      <c r="J35" s="28"/>
+      <c r="A35" s="29"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="29"/>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="28"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="28"/>
-      <c r="J36" s="28"/>
+      <c r="A36" s="29"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="29"/>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="28"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="28"/>
+      <c r="A37" s="29"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="28"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="28"/>
+      <c r="A38" s="29"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
+      <c r="I38" s="29"/>
+      <c r="J38" s="29"/>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="28"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="28"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="28"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="28"/>
-      <c r="J39" s="28"/>
+      <c r="A39" s="29"/>
+      <c r="B39" s="29"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="29"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="29"/>
+      <c r="I39" s="29"/>
+      <c r="J39" s="29"/>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="28"/>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="28"/>
-      <c r="J40" s="28"/>
+      <c r="A40" s="29"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="29"/>
+      <c r="J40" s="29"/>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="28"/>
-      <c r="B41" s="28"/>
-      <c r="C41" s="28"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="28"/>
-      <c r="I41" s="28"/>
-      <c r="J41" s="28"/>
+      <c r="A41" s="29"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="29"/>
+      <c r="I41" s="29"/>
+      <c r="J41" s="29"/>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="28"/>
-      <c r="B42" s="28"/>
-      <c r="C42" s="28"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="28"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="28"/>
-      <c r="I42" s="28"/>
-      <c r="J42" s="28"/>
+      <c r="A42" s="29"/>
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29"/>
+      <c r="I42" s="29"/>
+      <c r="J42" s="29"/>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="28"/>
-      <c r="B43" s="28"/>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="28"/>
-      <c r="J43" s="28"/>
+      <c r="A43" s="29"/>
+      <c r="B43" s="29"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29"/>
+      <c r="I43" s="29"/>
+      <c r="J43" s="29"/>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="28"/>
-      <c r="B44" s="28"/>
-      <c r="C44" s="28"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="28"/>
-      <c r="H44" s="28"/>
-      <c r="I44" s="28"/>
-      <c r="J44" s="28"/>
+      <c r="A44" s="29"/>
+      <c r="B44" s="29"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29"/>
+      <c r="H44" s="29"/>
+      <c r="I44" s="29"/>
+      <c r="J44" s="29"/>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="28"/>
-      <c r="B45" s="28"/>
-      <c r="C45" s="28"/>
-      <c r="D45" s="28"/>
-      <c r="E45" s="28"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="28"/>
-      <c r="H45" s="28"/>
-      <c r="I45" s="28"/>
-      <c r="J45" s="28"/>
+      <c r="A45" s="29"/>
+      <c r="B45" s="29"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="29"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="29"/>
+      <c r="H45" s="29"/>
+      <c r="I45" s="29"/>
+      <c r="J45" s="29"/>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -5176,484 +5212,484 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="11"/>
+      <c r="H1" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="28" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="13"/>
+      <c r="H2" s="14" t="n">
+        <v>45707</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="15"/>
+    </row>
+    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="30"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="15"/>
+    </row>
+    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="30"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="15"/>
+    </row>
+    <row r="5" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="10"/>
-      <c r="H1" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="27" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="29"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="12"/>
-      <c r="H2" s="13" t="n">
-        <v>45707</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="14"/>
-    </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="29"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="14"/>
-    </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="29"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="14"/>
-    </row>
-    <row r="5" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="30" t="s">
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="31" t="s">
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+    </row>
+    <row r="6" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31"/>
-    </row>
-    <row r="6" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="32" t="s">
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33"/>
+    </row>
+    <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="34"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+    </row>
+    <row r="8" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="34"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+    </row>
+    <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="34"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
+    </row>
+    <row r="10" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="34"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="34"/>
+    </row>
+    <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="34"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="34"/>
+    </row>
+    <row r="12" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="34"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="34"/>
+    </row>
+    <row r="13" customFormat="false" ht="271.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="34"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="34"/>
+    </row>
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="32"/>
-    </row>
-    <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="33"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
-    </row>
-    <row r="8" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="33"/>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-    </row>
-    <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="33"/>
-      <c r="B9" s="33"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-    </row>
-    <row r="10" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="33"/>
-      <c r="B10" s="33"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
-    </row>
-    <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="33"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
-    </row>
-    <row r="12" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="33"/>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-    </row>
-    <row r="13" customFormat="false" ht="271.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="33"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
-    </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="32" t="s">
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
-    </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="34" t="s">
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="35" t="s">
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="36" t="s">
+      <c r="J15" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="J15" s="37" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="35" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="34" t="s">
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="36" t="s">
+      <c r="E16" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="36" t="s">
+      <c r="F16" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="36" t="s">
+      <c r="G16" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="G16" s="36" t="s">
+      <c r="H16" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="H16" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
-    </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="39" t="s">
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="39"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="6" t="s">
+      <c r="E17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H17" s="18" t="s">
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+    </row>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-    </row>
-    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="39" t="s">
+      <c r="B18" s="40"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="39"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H18" s="18" t="s">
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+    </row>
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
-    </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="39" t="s">
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="39"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E19" s="6" t="s">
+      <c r="F19" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="G19" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="G19" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H19" s="18" t="s">
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+    </row>
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="I19" s="18"/>
-      <c r="J19" s="18"/>
-    </row>
-    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="39" t="s">
+      <c r="B20" s="40"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B20" s="39"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E20" s="6" t="s">
+      <c r="F20" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="G20" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="H20" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="H20" s="18" t="s">
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+    </row>
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="I20" s="18"/>
-      <c r="J20" s="18"/>
-    </row>
-    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="39" t="s">
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B21" s="39"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E21" s="6" t="s">
+      <c r="F21" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="G21" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H21" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="G21" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H21" s="18" t="s">
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+    </row>
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="I21" s="18"/>
-      <c r="J21" s="18"/>
-    </row>
-    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="39" t="s">
+      <c r="B22" s="40"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F22" s="6" t="s">
+      <c r="G22" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="H22" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="H22" s="18" t="s">
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+    </row>
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="I22" s="18"/>
-      <c r="J22" s="18"/>
-    </row>
-    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="39" t="s">
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F23" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B23" s="39"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F23" s="6" t="s">
+      <c r="G23" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="H23" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="H23" s="18" t="s">
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+    </row>
+    <row r="24" customFormat="false" ht="18.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="I23" s="18"/>
-      <c r="J23" s="18"/>
-    </row>
-    <row r="24" customFormat="false" ht="18.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="39" t="s">
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E24" s="6" t="s">
+      <c r="F24" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="G24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H24" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="G24" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H24" s="18" t="s">
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+    </row>
+    <row r="25" customFormat="false" ht="18.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="I24" s="18"/>
-      <c r="J24" s="18"/>
-    </row>
-    <row r="25" customFormat="false" ht="18.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="39" t="s">
+      <c r="B25" s="40"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B25" s="39"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E25" s="6" t="s">
+      <c r="F25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G25" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F25" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="G25" s="6" t="s">
+      <c r="H25" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="H25" s="18" t="s">
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+    </row>
+    <row r="26" customFormat="false" ht="18.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="I25" s="18"/>
-      <c r="J25" s="18"/>
-    </row>
-    <row r="26" customFormat="false" ht="18.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="40" t="s">
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="B26" s="40"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E26" s="12" t="s">
+      <c r="F26" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="G26" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="F26" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G26" s="12" t="s">
+      <c r="H26" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="H26" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="I26" s="24"/>
-      <c r="J26" s="24"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="25"/>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -6696,316 +6732,316 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="11"/>
+      <c r="H1" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="28" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="13"/>
+      <c r="H2" s="14" t="n">
+        <v>45707</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="15"/>
+    </row>
+    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="30"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="15"/>
+    </row>
+    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="30"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="15"/>
+    </row>
+    <row r="5" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="10"/>
-      <c r="H1" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="27" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="29"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="12"/>
-      <c r="H2" s="13" t="n">
-        <v>45707</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="14"/>
-    </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="29"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="14"/>
-    </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="29"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="14"/>
-    </row>
-    <row r="5" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="31" t="s">
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+    </row>
+    <row r="6" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33"/>
+    </row>
+    <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="34"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+    </row>
+    <row r="8" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="34"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+    </row>
+    <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="34"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
+    </row>
+    <row r="10" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="34"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="34"/>
+    </row>
+    <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="34"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="34"/>
+    </row>
+    <row r="12" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="34"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="34"/>
+    </row>
+    <row r="13" customFormat="false" ht="288.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="34"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="34"/>
+    </row>
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31"/>
-    </row>
-    <row r="6" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="32"/>
-    </row>
-    <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="33"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
-    </row>
-    <row r="8" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="33"/>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-    </row>
-    <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="33"/>
-      <c r="B9" s="33"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-    </row>
-    <row r="10" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="33"/>
-      <c r="B10" s="33"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
-    </row>
-    <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="33"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
-    </row>
-    <row r="12" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="33"/>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-    </row>
-    <row r="13" customFormat="false" ht="288.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="33"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
-    </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
-    </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="41" t="s">
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="J15" s="38" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="H16" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+    </row>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="40"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="J15" s="37" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="G16" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="H16" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
-    </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="39" t="s">
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+    </row>
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="41"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="39"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H17" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-    </row>
-    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="39" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="39"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H18" s="18" t="s">
+      <c r="E19" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="G19" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
-    </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="B19" s="40"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G19" s="12" t="s">
+      <c r="H19" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="H19" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I19" s="24"/>
-      <c r="J19" s="24"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -8040,316 +8076,316 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="11"/>
+      <c r="H1" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="28" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="13"/>
+      <c r="H2" s="14" t="n">
+        <v>45707</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="15"/>
+    </row>
+    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="30"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="15"/>
+    </row>
+    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="30"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="15"/>
+    </row>
+    <row r="5" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="10"/>
-      <c r="H1" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="27" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="29"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="12"/>
-      <c r="H2" s="13" t="n">
-        <v>45707</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="14"/>
-    </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="29"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="14"/>
-    </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="29"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="14"/>
-    </row>
-    <row r="5" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="31" t="s">
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+    </row>
+    <row r="6" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33"/>
+    </row>
+    <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="34"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+    </row>
+    <row r="8" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="34"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+    </row>
+    <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="34"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
+    </row>
+    <row r="10" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="34"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="34"/>
+    </row>
+    <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="34"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="34"/>
+    </row>
+    <row r="12" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="34"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="34"/>
+    </row>
+    <row r="13" customFormat="false" ht="288.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="34"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="34"/>
+    </row>
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="42" t="s">
         <v>91</v>
       </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31"/>
-    </row>
-    <row r="6" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="32"/>
-    </row>
-    <row r="7" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="33"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
-    </row>
-    <row r="8" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="33"/>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-    </row>
-    <row r="9" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="33"/>
-      <c r="B9" s="33"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-    </row>
-    <row r="10" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="33"/>
-      <c r="B10" s="33"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
-    </row>
-    <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="33"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
-    </row>
-    <row r="12" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="33"/>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-    </row>
-    <row r="13" customFormat="false" ht="288.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="33"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
-    </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
-    </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="41" t="s">
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="J15" s="38" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="H16" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+    </row>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="40"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="J15" s="37" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="G16" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="H16" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
-    </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="39" t="s">
+      <c r="I18" s="23"/>
+      <c r="J18" s="23"/>
+    </row>
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="41"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="39"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H17" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-    </row>
-    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="39" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="39"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H18" s="22" t="s">
+      <c r="E19" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="G19" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-    </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="B19" s="40"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G19" s="12" t="s">
+      <c r="H19" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="H19" s="42" t="s">
-        <v>95</v>
-      </c>
-      <c r="I19" s="42"/>
-      <c r="J19" s="42"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/詳細設計図/タスク編集機能_詳細設計図.xlsx
+++ b/詳細設計図/タスク編集機能_詳細設計図.xlsx
@@ -286,7 +286,7 @@
     <t xml:space="preserve">date</t>
   </si>
   <si>
-    <t xml:space="preserve">timeLimit</t>
+    <t xml:space="preserve">limitDate</t>
   </si>
   <si>
     <t xml:space="preserve">期限入力欄</t>
@@ -386,10 +386,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="m\月d\日"/>
-    <numFmt numFmtId="166" formatCode="m\月d\日"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -679,7 +678,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -882,9 +881,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>1036080</xdr:colOff>
+      <xdr:colOff>1035720</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>10080</xdr:rowOff>
+      <xdr:rowOff>9720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -898,7 +897,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="1542240"/>
-          <a:ext cx="9187560" cy="5535360"/>
+          <a:ext cx="9187200" cy="5535000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -925,9 +924,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>870480</xdr:colOff>
+      <xdr:colOff>870120</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>3437280</xdr:rowOff>
+      <xdr:rowOff>3436920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -941,7 +940,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="523800" y="1651320"/>
-          <a:ext cx="8051760" cy="4929120"/>
+          <a:ext cx="8051400" cy="4928760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -968,9 +967,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>216360</xdr:colOff>
+      <xdr:colOff>216000</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>3512160</xdr:rowOff>
+      <xdr:rowOff>3511800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -984,7 +983,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="693360" y="1716120"/>
-          <a:ext cx="8068320" cy="4939200"/>
+          <a:ext cx="8067960" cy="4938840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1011,9 +1010,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>514800</xdr:colOff>
+      <xdr:colOff>514440</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>3576600</xdr:rowOff>
+      <xdr:rowOff>3576240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1027,7 +1026,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="429840" y="1677600"/>
-          <a:ext cx="8236440" cy="5042160"/>
+          <a:ext cx="8236080" cy="5041800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
